--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/VIRGINIA_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/VIRGINIA_2018.xlsx
@@ -2605,7 +2605,7 @@
         <v>53</v>
       </c>
       <c r="D125">
-        <v>0.009142659996549939</v>
+        <v>0.009142659996549941</v>
       </c>
     </row>
     <row r="126">
@@ -2641,7 +2641,7 @@
         <v>53</v>
       </c>
       <c r="D127">
-        <v>0.009142659996549939</v>
+        <v>0.009142659996549941</v>
       </c>
     </row>
     <row r="128">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C230">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C524">
@@ -11040,7 +11040,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C594">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C627">
